--- a/ds/planejamento/4semestre/planos/Plano_de_Ensino_PSOF3.xlsx
+++ b/ds/planejamento/4semestre/planos/Plano_de_Ensino_PSOF3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Instrutor\Downloads\planos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFA8E467-9437-447C-90B4-AC5E08E17547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F48A674-C249-4FF5-B17A-4E25DAA67A5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -563,9 +563,6 @@
     <t>O que são soluções de TI? O que é uma IDE? O que é deploy? Quais são as boas práticas de deploy? Cite alguns serviços gratuitos o de podemos fazer daploy de aplicações Web?</t>
   </si>
   <si>
-    <t>Exposição dialogada, solução de situação desafiadora.</t>
-  </si>
-  <si>
     <t>Implementação de documentação e desenvolvimento de software com acompanhamento e tira dúvidas com instrutores, reuniões de verificação</t>
   </si>
   <si>
@@ -726,6 +723,9 @@
   </si>
   <si>
     <t>Cooperou para o sucesso das entregas e resultados do grupo</t>
+  </si>
+  <si>
+    <t>Exposição dialogada, solução de situação desafiadora, Projeto de software.</t>
   </si>
 </sst>
 </file>
@@ -1470,10 +1470,244 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1486,9 +1720,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1509,237 +1740,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -2019,134 +2019,134 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:27" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="123" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
+      <c r="B2" s="123"/>
+      <c r="C2" s="123"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="123"/>
+      <c r="F2" s="123"/>
+      <c r="G2" s="123"/>
+      <c r="H2" s="123"/>
+      <c r="I2" s="123"/>
+      <c r="J2" s="123"/>
     </row>
     <row r="3" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="40" t="s">
+      <c r="B3" s="132"/>
+      <c r="C3" s="124" t="s">
         <v>38</v>
       </c>
-      <c r="D3" s="41"/>
-      <c r="E3" s="45" t="s">
+      <c r="D3" s="125"/>
+      <c r="E3" s="128" t="s">
         <v>42</v>
       </c>
-      <c r="F3" s="46"/>
-      <c r="G3" s="39" t="s">
+      <c r="F3" s="129"/>
+      <c r="G3" s="108" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39" t="s">
+      <c r="H3" s="108"/>
+      <c r="I3" s="108" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="39"/>
+      <c r="J3" s="108"/>
     </row>
     <row r="4" spans="1:27" ht="15" x14ac:dyDescent="0.25">
-      <c r="A4" s="48"/>
-      <c r="B4" s="49"/>
-      <c r="C4" s="42"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="47" t="s">
+      <c r="A4" s="131"/>
+      <c r="B4" s="132"/>
+      <c r="C4" s="126"/>
+      <c r="D4" s="127"/>
+      <c r="E4" s="130" t="s">
         <v>41</v>
       </c>
-      <c r="F4" s="47"/>
-      <c r="G4" s="50" t="s">
+      <c r="F4" s="130"/>
+      <c r="G4" s="133" t="s">
         <v>43</v>
       </c>
-      <c r="H4" s="50"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="44"/>
+      <c r="H4" s="133"/>
+      <c r="I4" s="107"/>
+      <c r="J4" s="107"/>
     </row>
     <row r="5" spans="1:27" ht="15" x14ac:dyDescent="0.25">
-      <c r="A5" s="53" t="s">
+      <c r="A5" s="109" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="54"/>
-      <c r="C5" s="44" t="s">
+      <c r="B5" s="110"/>
+      <c r="C5" s="107" t="s">
         <v>58</v>
       </c>
-      <c r="D5" s="44"/>
-      <c r="E5" s="61" t="s">
+      <c r="D5" s="107"/>
+      <c r="E5" s="117" t="s">
         <v>44</v>
       </c>
-      <c r="F5" s="62"/>
-      <c r="G5" s="50" t="s">
+      <c r="F5" s="118"/>
+      <c r="G5" s="133" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="50"/>
+      <c r="H5" s="133"/>
+      <c r="I5" s="133"/>
+      <c r="J5" s="133"/>
     </row>
     <row r="6" spans="1:27" ht="15" x14ac:dyDescent="0.25">
-      <c r="A6" s="54"/>
-      <c r="B6" s="55"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="63" t="s">
+      <c r="A6" s="110"/>
+      <c r="B6" s="111"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="107"/>
+      <c r="E6" s="119" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="64"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
+      <c r="F6" s="120"/>
+      <c r="G6" s="107"/>
+      <c r="H6" s="107"/>
+      <c r="I6" s="107"/>
+      <c r="J6" s="107"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A7" s="53" t="s">
+      <c r="A7" s="109" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="54"/>
-      <c r="C7" s="56" t="s">
+      <c r="B7" s="110"/>
+      <c r="C7" s="112" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="56"/>
-      <c r="E7" s="65" t="s">
+      <c r="D7" s="112"/>
+      <c r="E7" s="121" t="s">
         <v>46</v>
       </c>
-      <c r="F7" s="66"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="44"/>
+      <c r="F7" s="122"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A8" s="54"/>
-      <c r="B8" s="55"/>
-      <c r="C8" s="56"/>
-      <c r="D8" s="56"/>
-      <c r="E8" s="65"/>
-      <c r="F8" s="66"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="44"/>
+      <c r="A8" s="110"/>
+      <c r="B8" s="111"/>
+      <c r="C8" s="112"/>
+      <c r="D8" s="112"/>
+      <c r="E8" s="121"/>
+      <c r="F8" s="122"/>
+      <c r="G8" s="107"/>
+      <c r="H8" s="107"/>
+      <c r="I8" s="107"/>
+      <c r="J8" s="107"/>
     </row>
     <row r="9" spans="1:27" ht="18" x14ac:dyDescent="0.25">
-      <c r="A9" s="57" t="s">
+      <c r="A9" s="113" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="57"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="57"/>
-      <c r="J9" s="57"/>
+      <c r="B9" s="113"/>
+      <c r="C9" s="113"/>
+      <c r="D9" s="113"/>
+      <c r="E9" s="113"/>
+      <c r="F9" s="113"/>
+      <c r="G9" s="113"/>
+      <c r="H9" s="113"/>
+      <c r="I9" s="113"/>
+      <c r="J9" s="113"/>
     </row>
     <row r="10" spans="1:27" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" s="24" t="s">
@@ -2167,14 +2167,14 @@
       <c r="F10" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="G10" s="58" t="s">
+      <c r="G10" s="114" t="s">
         <v>8</v>
       </c>
-      <c r="H10" s="58"/>
-      <c r="I10" s="58" t="s">
+      <c r="H10" s="114"/>
+      <c r="I10" s="114" t="s">
         <v>9</v>
       </c>
-      <c r="J10" s="58"/>
+      <c r="J10" s="114"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -2209,17 +2209,17 @@
       <c r="E11" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="119" t="s">
+      <c r="F11" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="G11" s="59" t="s">
+      <c r="G11" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="H11" s="60"/>
-      <c r="I11" s="51" t="s">
-        <v>81</v>
+      <c r="H11" s="65"/>
+      <c r="I11" s="115" t="s">
+        <v>135</v>
       </c>
-      <c r="J11" s="52"/>
+      <c r="J11" s="116"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -2254,15 +2254,15 @@
       <c r="E12" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="F12" s="120"/>
-      <c r="G12" s="59" t="s">
-        <v>87</v>
+      <c r="F12" s="60"/>
+      <c r="G12" s="64" t="s">
+        <v>86</v>
       </c>
-      <c r="H12" s="60"/>
-      <c r="I12" s="126" t="s">
-        <v>82</v>
+      <c r="H12" s="65"/>
+      <c r="I12" s="62" t="s">
+        <v>81</v>
       </c>
-      <c r="J12" s="127"/>
+      <c r="J12" s="63"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
@@ -2297,15 +2297,15 @@
       <c r="E13" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="F13" s="120"/>
-      <c r="G13" s="59" t="s">
-        <v>86</v>
+      <c r="F13" s="60"/>
+      <c r="G13" s="64" t="s">
+        <v>85</v>
       </c>
-      <c r="H13" s="60"/>
-      <c r="I13" s="126" t="s">
-        <v>82</v>
+      <c r="H13" s="65"/>
+      <c r="I13" s="62" t="s">
+        <v>81</v>
       </c>
-      <c r="J13" s="127"/>
+      <c r="J13" s="63"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
@@ -2340,15 +2340,15 @@
       <c r="E14" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="F14" s="120"/>
-      <c r="G14" s="59" t="s">
-        <v>85</v>
+      <c r="F14" s="60"/>
+      <c r="G14" s="64" t="s">
+        <v>84</v>
       </c>
-      <c r="H14" s="60"/>
-      <c r="I14" s="126" t="s">
-        <v>82</v>
+      <c r="H14" s="65"/>
+      <c r="I14" s="62" t="s">
+        <v>81</v>
       </c>
-      <c r="J14" s="127"/>
+      <c r="J14" s="63"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
@@ -2383,15 +2383,15 @@
       <c r="E15" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="F15" s="121"/>
-      <c r="G15" s="59" t="s">
-        <v>84</v>
-      </c>
-      <c r="H15" s="60"/>
-      <c r="I15" s="126" t="s">
+      <c r="F15" s="61"/>
+      <c r="G15" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="J15" s="127"/>
+      <c r="H15" s="65"/>
+      <c r="I15" s="62" t="s">
+        <v>82</v>
+      </c>
+      <c r="J15" s="63"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
@@ -2422,10 +2422,10 @@
       <c r="D16" s="14"/>
       <c r="E16" s="14"/>
       <c r="F16" s="15"/>
-      <c r="G16" s="122"/>
-      <c r="H16" s="123"/>
-      <c r="I16" s="124"/>
-      <c r="J16" s="125"/>
+      <c r="G16" s="66"/>
+      <c r="H16" s="67"/>
+      <c r="I16" s="68"/>
+      <c r="J16" s="69"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -2445,18 +2445,18 @@
       <c r="AA16" s="1"/>
     </row>
     <row r="17" spans="1:27" ht="23.25" x14ac:dyDescent="0.2">
-      <c r="A17" s="83" t="s">
+      <c r="A17" s="82" t="s">
         <v>55</v>
       </c>
-      <c r="B17" s="84"/>
-      <c r="C17" s="84"/>
-      <c r="D17" s="84"/>
-      <c r="E17" s="84"/>
-      <c r="F17" s="84"/>
-      <c r="G17" s="84"/>
-      <c r="H17" s="84"/>
-      <c r="I17" s="84"/>
-      <c r="J17" s="85"/>
+      <c r="B17" s="83"/>
+      <c r="C17" s="83"/>
+      <c r="D17" s="83"/>
+      <c r="E17" s="83"/>
+      <c r="F17" s="83"/>
+      <c r="G17" s="83"/>
+      <c r="H17" s="83"/>
+      <c r="I17" s="83"/>
+      <c r="J17" s="84"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -2476,18 +2476,18 @@
       <c r="AA17" s="1"/>
     </row>
     <row r="18" spans="1:27" ht="18" x14ac:dyDescent="0.2">
-      <c r="A18" s="86" t="s">
+      <c r="A18" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="86"/>
-      <c r="C18" s="86"/>
-      <c r="D18" s="86"/>
-      <c r="E18" s="86"/>
-      <c r="F18" s="86"/>
-      <c r="G18" s="86"/>
-      <c r="H18" s="86"/>
-      <c r="I18" s="86"/>
-      <c r="J18" s="86"/>
+      <c r="B18" s="54"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="54"/>
+      <c r="H18" s="54"/>
+      <c r="I18" s="54"/>
+      <c r="J18" s="54"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -2507,18 +2507,18 @@
       <c r="AA18" s="1"/>
     </row>
     <row r="19" spans="1:27" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="78" t="s">
+      <c r="A19" s="70" t="s">
         <v>71</v>
       </c>
-      <c r="B19" s="78"/>
-      <c r="C19" s="78"/>
-      <c r="D19" s="78"/>
-      <c r="E19" s="78"/>
-      <c r="F19" s="78"/>
-      <c r="G19" s="78"/>
-      <c r="H19" s="78"/>
-      <c r="I19" s="78"/>
-      <c r="J19" s="78"/>
+      <c r="B19" s="70"/>
+      <c r="C19" s="70"/>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70"/>
+      <c r="I19" s="70"/>
+      <c r="J19" s="70"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -2538,18 +2538,18 @@
       <c r="AA19" s="1"/>
     </row>
     <row r="20" spans="1:27" ht="18" x14ac:dyDescent="0.2">
-      <c r="A20" s="86" t="s">
+      <c r="A20" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="86"/>
-      <c r="C20" s="86"/>
-      <c r="D20" s="86"/>
-      <c r="E20" s="86"/>
-      <c r="F20" s="86"/>
-      <c r="G20" s="86"/>
-      <c r="H20" s="86"/>
-      <c r="I20" s="86"/>
-      <c r="J20" s="86"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="54"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="54"/>
+      <c r="H20" s="54"/>
+      <c r="I20" s="54"/>
+      <c r="J20" s="54"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -2569,18 +2569,18 @@
       <c r="AA20" s="1"/>
     </row>
     <row r="21" spans="1:27" ht="279.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="82" t="s">
+      <c r="A21" s="106" t="s">
         <v>72</v>
       </c>
-      <c r="B21" s="82"/>
-      <c r="C21" s="82"/>
-      <c r="D21" s="82"/>
-      <c r="E21" s="82"/>
-      <c r="F21" s="82"/>
-      <c r="G21" s="82"/>
-      <c r="H21" s="82"/>
-      <c r="I21" s="82"/>
-      <c r="J21" s="82"/>
+      <c r="B21" s="106"/>
+      <c r="C21" s="106"/>
+      <c r="D21" s="106"/>
+      <c r="E21" s="106"/>
+      <c r="F21" s="106"/>
+      <c r="G21" s="106"/>
+      <c r="H21" s="106"/>
+      <c r="I21" s="106"/>
+      <c r="J21" s="106"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
       <c r="O21" s="1"/>
@@ -2596,18 +2596,18 @@
       <c r="AA21" s="1"/>
     </row>
     <row r="22" spans="1:27" ht="18" x14ac:dyDescent="0.2">
-      <c r="A22" s="86" t="s">
+      <c r="A22" s="54" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="86"/>
-      <c r="C22" s="86"/>
-      <c r="D22" s="86"/>
-      <c r="E22" s="86"/>
-      <c r="F22" s="86"/>
-      <c r="G22" s="86"/>
-      <c r="H22" s="86"/>
-      <c r="I22" s="86"/>
-      <c r="J22" s="86"/>
+      <c r="B22" s="54"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="54"/>
+      <c r="H22" s="54"/>
+      <c r="I22" s="54"/>
+      <c r="J22" s="54"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -2627,18 +2627,18 @@
       <c r="AA22" s="1"/>
     </row>
     <row r="23" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="78" t="s">
+      <c r="A23" s="70" t="s">
         <v>54</v>
       </c>
-      <c r="B23" s="78"/>
-      <c r="C23" s="78"/>
-      <c r="D23" s="78"/>
-      <c r="E23" s="78"/>
-      <c r="F23" s="78"/>
-      <c r="G23" s="78"/>
-      <c r="H23" s="78"/>
-      <c r="I23" s="78"/>
-      <c r="J23" s="78"/>
+      <c r="B23" s="70"/>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70"/>
+      <c r="I23" s="70"/>
+      <c r="J23" s="70"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
@@ -2658,18 +2658,18 @@
       <c r="AA23" s="1"/>
     </row>
     <row r="24" spans="1:27" ht="23.25" x14ac:dyDescent="0.2">
-      <c r="A24" s="79" t="s">
+      <c r="A24" s="104" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="79"/>
-      <c r="C24" s="79"/>
-      <c r="D24" s="79"/>
-      <c r="E24" s="79"/>
-      <c r="F24" s="79"/>
-      <c r="G24" s="79"/>
-      <c r="H24" s="79"/>
-      <c r="I24" s="79"/>
-      <c r="J24" s="79"/>
+      <c r="B24" s="104"/>
+      <c r="C24" s="104"/>
+      <c r="D24" s="104"/>
+      <c r="E24" s="104"/>
+      <c r="F24" s="104"/>
+      <c r="G24" s="104"/>
+      <c r="H24" s="104"/>
+      <c r="I24" s="104"/>
+      <c r="J24" s="104"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
@@ -2689,22 +2689,22 @@
       <c r="AA24" s="1"/>
     </row>
     <row r="25" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="75" t="s">
+      <c r="A25" s="101" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="76"/>
-      <c r="C25" s="76"/>
-      <c r="D25" s="77" t="s">
+      <c r="B25" s="102"/>
+      <c r="C25" s="102"/>
+      <c r="D25" s="103" t="s">
         <v>10</v>
       </c>
-      <c r="E25" s="77"/>
-      <c r="F25" s="77"/>
-      <c r="G25" s="80" t="s">
+      <c r="E25" s="103"/>
+      <c r="F25" s="103"/>
+      <c r="G25" s="78" t="s">
         <v>34</v>
       </c>
-      <c r="H25" s="81"/>
-      <c r="I25" s="81"/>
-      <c r="J25" s="81"/>
+      <c r="H25" s="105"/>
+      <c r="I25" s="105"/>
+      <c r="J25" s="105"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -2724,12 +2724,12 @@
       <c r="AA25" s="1"/>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A26" s="76"/>
-      <c r="B26" s="76"/>
-      <c r="C26" s="76"/>
-      <c r="D26" s="77"/>
-      <c r="E26" s="77"/>
-      <c r="F26" s="77"/>
+      <c r="A26" s="102"/>
+      <c r="B26" s="102"/>
+      <c r="C26" s="102"/>
+      <c r="D26" s="103"/>
+      <c r="E26" s="103"/>
+      <c r="F26" s="103"/>
       <c r="G26" s="21">
         <v>1</v>
       </c>
@@ -2761,18 +2761,18 @@
       <c r="AA26" s="1"/>
     </row>
     <row r="27" spans="1:27" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="117" t="s">
+      <c r="A27" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="B27" s="128" t="s">
+      <c r="B27" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="129"/>
-      <c r="D27" s="70" t="s">
-        <v>123</v>
+      <c r="C27" s="47"/>
+      <c r="D27" s="71" t="s">
+        <v>122</v>
       </c>
-      <c r="E27" s="73"/>
-      <c r="F27" s="74"/>
+      <c r="E27" s="72"/>
+      <c r="F27" s="73"/>
       <c r="G27" s="7"/>
       <c r="H27" s="18"/>
       <c r="I27" s="19"/>
@@ -2796,14 +2796,14 @@
       <c r="AA27" s="1"/>
     </row>
     <row r="28" spans="1:27" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="118"/>
-      <c r="B28" s="130"/>
-      <c r="C28" s="131"/>
-      <c r="D28" s="67" t="s">
-        <v>124</v>
+      <c r="A28" s="58"/>
+      <c r="B28" s="48"/>
+      <c r="C28" s="49"/>
+      <c r="D28" s="43" t="s">
+        <v>123</v>
       </c>
-      <c r="E28" s="68"/>
-      <c r="F28" s="69"/>
+      <c r="E28" s="44"/>
+      <c r="F28" s="45"/>
       <c r="G28" s="7"/>
       <c r="H28" s="18"/>
       <c r="I28" s="14"/>
@@ -2827,16 +2827,16 @@
       <c r="AA28" s="1"/>
     </row>
     <row r="29" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="118"/>
-      <c r="B29" s="128" t="s">
+      <c r="A29" s="58"/>
+      <c r="B29" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="C29" s="129"/>
-      <c r="D29" s="70" t="s">
-        <v>125</v>
+      <c r="C29" s="47"/>
+      <c r="D29" s="71" t="s">
+        <v>124</v>
       </c>
-      <c r="E29" s="71"/>
-      <c r="F29" s="72"/>
+      <c r="E29" s="99"/>
+      <c r="F29" s="100"/>
       <c r="G29" s="7"/>
       <c r="H29" s="18"/>
       <c r="I29" s="14"/>
@@ -2860,14 +2860,14 @@
       <c r="AA29" s="1"/>
     </row>
     <row r="30" spans="1:27" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="118"/>
-      <c r="B30" s="130"/>
-      <c r="C30" s="131"/>
-      <c r="D30" s="67" t="s">
-        <v>126</v>
+      <c r="A30" s="58"/>
+      <c r="B30" s="48"/>
+      <c r="C30" s="49"/>
+      <c r="D30" s="43" t="s">
+        <v>125</v>
       </c>
-      <c r="E30" s="68"/>
-      <c r="F30" s="69"/>
+      <c r="E30" s="44"/>
+      <c r="F30" s="45"/>
       <c r="G30" s="7"/>
       <c r="H30" s="18"/>
       <c r="I30" s="14"/>
@@ -2891,16 +2891,16 @@
       <c r="AA30" s="1"/>
     </row>
     <row r="31" spans="1:27" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="118"/>
-      <c r="B31" s="128" t="s">
+      <c r="A31" s="58"/>
+      <c r="B31" s="46" t="s">
         <v>68</v>
       </c>
-      <c r="C31" s="129"/>
-      <c r="D31" s="114" t="s">
-        <v>127</v>
+      <c r="C31" s="47"/>
+      <c r="D31" s="40" t="s">
+        <v>126</v>
       </c>
-      <c r="E31" s="115"/>
-      <c r="F31" s="116"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="42"/>
       <c r="G31" s="7"/>
       <c r="H31" s="18"/>
       <c r="I31" s="14"/>
@@ -2924,14 +2924,14 @@
       <c r="AA31" s="1"/>
     </row>
     <row r="32" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="118"/>
-      <c r="B32" s="130"/>
-      <c r="C32" s="131"/>
-      <c r="D32" s="67" t="s">
-        <v>128</v>
+      <c r="A32" s="58"/>
+      <c r="B32" s="48"/>
+      <c r="C32" s="49"/>
+      <c r="D32" s="43" t="s">
+        <v>127</v>
       </c>
-      <c r="E32" s="68"/>
-      <c r="F32" s="69"/>
+      <c r="E32" s="44"/>
+      <c r="F32" s="45"/>
       <c r="G32" s="7"/>
       <c r="H32" s="18"/>
       <c r="I32" s="14"/>
@@ -2955,16 +2955,16 @@
       <c r="AA32" s="1"/>
     </row>
     <row r="33" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="118"/>
-      <c r="B33" s="128" t="s">
+      <c r="A33" s="58"/>
+      <c r="B33" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="C33" s="129"/>
-      <c r="D33" s="70" t="s">
-        <v>129</v>
+      <c r="C33" s="47"/>
+      <c r="D33" s="71" t="s">
+        <v>128</v>
       </c>
-      <c r="E33" s="73"/>
-      <c r="F33" s="74"/>
+      <c r="E33" s="72"/>
+      <c r="F33" s="73"/>
       <c r="G33" s="7"/>
       <c r="H33" s="18"/>
       <c r="I33" s="14"/>
@@ -2988,14 +2988,14 @@
       <c r="AA33" s="1"/>
     </row>
     <row r="34" spans="1:27" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="118"/>
-      <c r="B34" s="130"/>
-      <c r="C34" s="131"/>
-      <c r="D34" s="67" t="s">
-        <v>130</v>
+      <c r="A34" s="58"/>
+      <c r="B34" s="48"/>
+      <c r="C34" s="49"/>
+      <c r="D34" s="43" t="s">
+        <v>129</v>
       </c>
-      <c r="E34" s="68"/>
-      <c r="F34" s="69"/>
+      <c r="E34" s="44"/>
+      <c r="F34" s="45"/>
       <c r="G34" s="7"/>
       <c r="H34" s="18"/>
       <c r="I34" s="14"/>
@@ -3019,16 +3019,16 @@
       <c r="AA34" s="1"/>
     </row>
     <row r="35" spans="1:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="118"/>
-      <c r="B35" s="128" t="s">
+      <c r="A35" s="58"/>
+      <c r="B35" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="C35" s="129"/>
-      <c r="D35" s="114" t="s">
-        <v>131</v>
+      <c r="C35" s="47"/>
+      <c r="D35" s="40" t="s">
+        <v>130</v>
       </c>
-      <c r="E35" s="115"/>
-      <c r="F35" s="116"/>
+      <c r="E35" s="41"/>
+      <c r="F35" s="42"/>
       <c r="G35" s="7"/>
       <c r="H35" s="18"/>
       <c r="I35" s="14"/>
@@ -3052,14 +3052,14 @@
       <c r="AA35" s="1"/>
     </row>
     <row r="36" spans="1:27" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="118"/>
-      <c r="B36" s="130"/>
-      <c r="C36" s="131"/>
-      <c r="D36" s="67" t="s">
-        <v>132</v>
+      <c r="A36" s="58"/>
+      <c r="B36" s="48"/>
+      <c r="C36" s="49"/>
+      <c r="D36" s="43" t="s">
+        <v>131</v>
       </c>
-      <c r="E36" s="68"/>
-      <c r="F36" s="69"/>
+      <c r="E36" s="44"/>
+      <c r="F36" s="45"/>
       <c r="G36" s="7"/>
       <c r="H36" s="18"/>
       <c r="I36" s="14"/>
@@ -3083,18 +3083,18 @@
       <c r="AA36" s="1"/>
     </row>
     <row r="37" spans="1:27" ht="15" x14ac:dyDescent="0.2">
-      <c r="A37" s="104" t="s">
+      <c r="A37" s="97" t="s">
         <v>27</v>
       </c>
-      <c r="B37" s="106" t="s">
-        <v>88</v>
+      <c r="B37" s="55" t="s">
+        <v>87</v>
       </c>
-      <c r="C37" s="107"/>
-      <c r="D37" s="67" t="s">
-        <v>133</v>
+      <c r="C37" s="56"/>
+      <c r="D37" s="43" t="s">
+        <v>132</v>
       </c>
-      <c r="E37" s="68"/>
-      <c r="F37" s="69"/>
+      <c r="E37" s="44"/>
+      <c r="F37" s="45"/>
       <c r="G37" s="7"/>
       <c r="H37" s="18"/>
       <c r="I37" s="14"/>
@@ -3118,16 +3118,16 @@
       <c r="AA37" s="1"/>
     </row>
     <row r="38" spans="1:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="105"/>
-      <c r="B38" s="106" t="s">
-        <v>89</v>
+      <c r="A38" s="98"/>
+      <c r="B38" s="55" t="s">
+        <v>88</v>
       </c>
-      <c r="C38" s="107"/>
-      <c r="D38" s="67" t="s">
-        <v>134</v>
+      <c r="C38" s="56"/>
+      <c r="D38" s="43" t="s">
+        <v>133</v>
       </c>
-      <c r="E38" s="68"/>
-      <c r="F38" s="69"/>
+      <c r="E38" s="44"/>
+      <c r="F38" s="45"/>
       <c r="G38" s="7"/>
       <c r="H38" s="18"/>
       <c r="I38" s="14"/>
@@ -3151,16 +3151,16 @@
       <c r="AA38" s="1"/>
     </row>
     <row r="39" spans="1:27" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="105"/>
-      <c r="B39" s="106" t="s">
-        <v>90</v>
+      <c r="A39" s="98"/>
+      <c r="B39" s="55" t="s">
+        <v>89</v>
       </c>
-      <c r="C39" s="107"/>
-      <c r="D39" s="67" t="s">
-        <v>135</v>
+      <c r="C39" s="56"/>
+      <c r="D39" s="43" t="s">
+        <v>134</v>
       </c>
-      <c r="E39" s="68"/>
-      <c r="F39" s="69"/>
+      <c r="E39" s="44"/>
+      <c r="F39" s="45"/>
       <c r="G39" s="7"/>
       <c r="H39" s="18"/>
       <c r="I39" s="14"/>
@@ -3184,14 +3184,14 @@
       <c r="AA39" s="1"/>
     </row>
     <row r="40" spans="1:27" ht="15" x14ac:dyDescent="0.25">
-      <c r="A40" s="103"/>
-      <c r="B40" s="103"/>
-      <c r="C40" s="103"/>
-      <c r="D40" s="103"/>
-      <c r="E40" s="103"/>
-      <c r="F40" s="103"/>
-      <c r="G40" s="103"/>
-      <c r="H40" s="103"/>
+      <c r="A40" s="96"/>
+      <c r="B40" s="96"/>
+      <c r="C40" s="96"/>
+      <c r="D40" s="96"/>
+      <c r="E40" s="96"/>
+      <c r="F40" s="96"/>
+      <c r="G40" s="96"/>
+      <c r="H40" s="96"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
@@ -3213,18 +3213,18 @@
       <c r="AA40" s="1"/>
     </row>
     <row r="41" spans="1:27" ht="15" x14ac:dyDescent="0.25">
-      <c r="A41" s="99" t="s">
+      <c r="A41" s="92" t="s">
         <v>12</v>
       </c>
-      <c r="B41" s="100"/>
-      <c r="C41" s="100"/>
-      <c r="D41" s="100"/>
-      <c r="E41" s="101"/>
-      <c r="F41" s="102" t="s">
+      <c r="B41" s="93"/>
+      <c r="C41" s="93"/>
+      <c r="D41" s="93"/>
+      <c r="E41" s="94"/>
+      <c r="F41" s="95" t="s">
         <v>13</v>
       </c>
-      <c r="G41" s="100"/>
-      <c r="H41" s="101"/>
+      <c r="G41" s="93"/>
+      <c r="H41" s="94"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
@@ -3249,17 +3249,17 @@
       <c r="A42" s="8">
         <v>10</v>
       </c>
-      <c r="B42" s="91" t="s">
+      <c r="B42" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="C42" s="88"/>
-      <c r="D42" s="88"/>
-      <c r="E42" s="89"/>
-      <c r="F42" s="90">
+      <c r="C42" s="51"/>
+      <c r="D42" s="51"/>
+      <c r="E42" s="52"/>
+      <c r="F42" s="53">
         <v>100</v>
       </c>
-      <c r="G42" s="88"/>
-      <c r="H42" s="89"/>
+      <c r="G42" s="51"/>
+      <c r="H42" s="52"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
@@ -3284,17 +3284,17 @@
       <c r="A43" s="8">
         <v>9</v>
       </c>
-      <c r="B43" s="98" t="s">
+      <c r="B43" s="50" t="s">
         <v>79</v>
       </c>
-      <c r="C43" s="88"/>
-      <c r="D43" s="88"/>
-      <c r="E43" s="89"/>
-      <c r="F43" s="90">
+      <c r="C43" s="51"/>
+      <c r="D43" s="51"/>
+      <c r="E43" s="52"/>
+      <c r="F43" s="53">
         <v>95</v>
       </c>
-      <c r="G43" s="88"/>
-      <c r="H43" s="89"/>
+      <c r="G43" s="51"/>
+      <c r="H43" s="52"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
@@ -3319,17 +3319,17 @@
       <c r="A44" s="8">
         <v>8</v>
       </c>
-      <c r="B44" s="98" t="s">
+      <c r="B44" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="C44" s="88"/>
-      <c r="D44" s="88"/>
-      <c r="E44" s="89"/>
-      <c r="F44" s="90">
+      <c r="C44" s="51"/>
+      <c r="D44" s="51"/>
+      <c r="E44" s="52"/>
+      <c r="F44" s="53">
         <v>90</v>
       </c>
-      <c r="G44" s="88"/>
-      <c r="H44" s="89"/>
+      <c r="G44" s="51"/>
+      <c r="H44" s="52"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
@@ -3354,17 +3354,17 @@
       <c r="A45" s="8">
         <v>7</v>
       </c>
-      <c r="B45" s="98" t="s">
+      <c r="B45" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="C45" s="88"/>
-      <c r="D45" s="88"/>
-      <c r="E45" s="89"/>
-      <c r="F45" s="90">
+      <c r="C45" s="51"/>
+      <c r="D45" s="51"/>
+      <c r="E45" s="52"/>
+      <c r="F45" s="53">
         <v>85</v>
       </c>
-      <c r="G45" s="88"/>
-      <c r="H45" s="89"/>
+      <c r="G45" s="51"/>
+      <c r="H45" s="52"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
@@ -3389,17 +3389,17 @@
       <c r="A46" s="8">
         <v>6</v>
       </c>
-      <c r="B46" s="98" t="s">
+      <c r="B46" s="50" t="s">
         <v>76</v>
       </c>
-      <c r="C46" s="88"/>
-      <c r="D46" s="88"/>
-      <c r="E46" s="89"/>
-      <c r="F46" s="90">
+      <c r="C46" s="51"/>
+      <c r="D46" s="51"/>
+      <c r="E46" s="52"/>
+      <c r="F46" s="53">
         <v>80</v>
       </c>
-      <c r="G46" s="88"/>
-      <c r="H46" s="89"/>
+      <c r="G46" s="51"/>
+      <c r="H46" s="52"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
@@ -3424,17 +3424,17 @@
       <c r="A47" s="8">
         <v>5</v>
       </c>
-      <c r="B47" s="92" t="s">
+      <c r="B47" s="86" t="s">
         <v>75</v>
       </c>
-      <c r="C47" s="93"/>
-      <c r="D47" s="93"/>
-      <c r="E47" s="94"/>
-      <c r="F47" s="95">
+      <c r="C47" s="87"/>
+      <c r="D47" s="87"/>
+      <c r="E47" s="88"/>
+      <c r="F47" s="89">
         <v>75</v>
       </c>
-      <c r="G47" s="96"/>
-      <c r="H47" s="97"/>
+      <c r="G47" s="90"/>
+      <c r="H47" s="91"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
@@ -3459,17 +3459,17 @@
       <c r="A48" s="8">
         <v>4</v>
       </c>
-      <c r="B48" s="92" t="s">
+      <c r="B48" s="86" t="s">
         <v>74</v>
       </c>
-      <c r="C48" s="93"/>
-      <c r="D48" s="93"/>
-      <c r="E48" s="94"/>
-      <c r="F48" s="95">
+      <c r="C48" s="87"/>
+      <c r="D48" s="87"/>
+      <c r="E48" s="88"/>
+      <c r="F48" s="89">
         <v>70</v>
       </c>
-      <c r="G48" s="96"/>
-      <c r="H48" s="97"/>
+      <c r="G48" s="90"/>
+      <c r="H48" s="91"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
@@ -3494,17 +3494,17 @@
       <c r="A49" s="8">
         <v>3</v>
       </c>
-      <c r="B49" s="98" t="s">
+      <c r="B49" s="50" t="s">
         <v>73</v>
       </c>
-      <c r="C49" s="88"/>
-      <c r="D49" s="88"/>
-      <c r="E49" s="89"/>
-      <c r="F49" s="90">
+      <c r="C49" s="51"/>
+      <c r="D49" s="51"/>
+      <c r="E49" s="52"/>
+      <c r="F49" s="53">
         <v>60</v>
       </c>
-      <c r="G49" s="88"/>
-      <c r="H49" s="89"/>
+      <c r="G49" s="51"/>
+      <c r="H49" s="52"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
@@ -3529,17 +3529,17 @@
       <c r="A50" s="8">
         <v>2</v>
       </c>
-      <c r="B50" s="87" t="s">
+      <c r="B50" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="C50" s="88"/>
-      <c r="D50" s="88"/>
-      <c r="E50" s="89"/>
-      <c r="F50" s="90">
+      <c r="C50" s="51"/>
+      <c r="D50" s="51"/>
+      <c r="E50" s="52"/>
+      <c r="F50" s="53">
         <v>50</v>
       </c>
-      <c r="G50" s="88"/>
-      <c r="H50" s="89"/>
+      <c r="G50" s="51"/>
+      <c r="H50" s="52"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
@@ -3564,17 +3564,17 @@
       <c r="A51" s="8">
         <v>1</v>
       </c>
-      <c r="B51" s="91" t="s">
+      <c r="B51" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="C51" s="88"/>
-      <c r="D51" s="88"/>
-      <c r="E51" s="89"/>
-      <c r="F51" s="90">
+      <c r="C51" s="51"/>
+      <c r="D51" s="51"/>
+      <c r="E51" s="52"/>
+      <c r="F51" s="53">
         <v>30</v>
       </c>
-      <c r="G51" s="88"/>
-      <c r="H51" s="89"/>
+      <c r="G51" s="51"/>
+      <c r="H51" s="52"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
@@ -3666,16 +3666,16 @@
       <c r="D54" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E54" s="109">
+      <c r="E54" s="76">
         <v>1</v>
       </c>
-      <c r="F54" s="109">
+      <c r="F54" s="76">
         <v>0</v>
       </c>
-      <c r="G54" s="80" t="s">
+      <c r="G54" s="78" t="s">
         <v>56</v>
       </c>
-      <c r="H54" s="112" t="s">
+      <c r="H54" s="80" t="s">
         <v>57</v>
       </c>
       <c r="I54" s="1"/>
@@ -3705,10 +3705,10 @@
       <c r="D55" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="E55" s="110"/>
-      <c r="F55" s="110"/>
-      <c r="G55" s="111"/>
-      <c r="H55" s="113"/>
+      <c r="E55" s="77"/>
+      <c r="F55" s="77"/>
+      <c r="G55" s="79"/>
+      <c r="H55" s="81"/>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
@@ -3730,18 +3730,18 @@
       <c r="AA55" s="1"/>
     </row>
     <row r="56" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A56" s="108" t="s">
+      <c r="A56" s="74" t="s">
         <v>36</v>
       </c>
-      <c r="B56" s="108"/>
-      <c r="C56" s="108"/>
-      <c r="D56" s="108"/>
-      <c r="E56" s="108"/>
-      <c r="F56" s="108"/>
-      <c r="G56" s="108"/>
-      <c r="H56" s="108"/>
-      <c r="I56" s="108"/>
-      <c r="J56" s="108"/>
+      <c r="B56" s="74"/>
+      <c r="C56" s="74"/>
+      <c r="D56" s="74"/>
+      <c r="E56" s="74"/>
+      <c r="F56" s="74"/>
+      <c r="G56" s="74"/>
+      <c r="H56" s="74"/>
+      <c r="I56" s="74"/>
+      <c r="J56" s="74"/>
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
       <c r="M56" s="1"/>
@@ -29891,48 +29891,39 @@
     </row>
   </sheetData>
   <mergeCells count="96">
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="B35:C36"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="F44:H44"/>
-    <mergeCell ref="B33:C34"/>
-    <mergeCell ref="A22:J22"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="A27:A36"/>
-    <mergeCell ref="F11:F15"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="B27:C28"/>
-    <mergeCell ref="B29:C30"/>
-    <mergeCell ref="B31:C32"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="A56:J56"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="F51:H51"/>
-    <mergeCell ref="E54:E55"/>
-    <mergeCell ref="F54:F55"/>
-    <mergeCell ref="G54:G55"/>
-    <mergeCell ref="H54:H55"/>
-    <mergeCell ref="A17:J17"/>
-    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="E7:F8"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="C3:D4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="A21:J21"/>
+    <mergeCell ref="G6:J8"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="A7:B8"/>
+    <mergeCell ref="C5:D6"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="A5:B6"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="A25:C26"/>
+    <mergeCell ref="D25:F26"/>
+    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="G25:J25"/>
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="B50:E50"/>
     <mergeCell ref="F50:H50"/>
@@ -29949,44 +29940,53 @@
     <mergeCell ref="B45:E45"/>
     <mergeCell ref="F45:H45"/>
     <mergeCell ref="D30:F30"/>
+    <mergeCell ref="A56:J56"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="F51:H51"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="F54:F55"/>
+    <mergeCell ref="G54:G55"/>
+    <mergeCell ref="H54:H55"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="F11:F15"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="B33:C34"/>
+    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="A27:A36"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="B27:C28"/>
+    <mergeCell ref="B29:C30"/>
+    <mergeCell ref="B31:C32"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="A37:A39"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="B35:C36"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="F44:H44"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="D39:F39"/>
     <mergeCell ref="A41:E41"/>
     <mergeCell ref="F41:H41"/>
     <mergeCell ref="A40:H40"/>
-    <mergeCell ref="A37:A39"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="A25:C26"/>
-    <mergeCell ref="D25:F26"/>
-    <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="G25:J25"/>
-    <mergeCell ref="A21:J21"/>
-    <mergeCell ref="G6:J8"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="A7:B8"/>
-    <mergeCell ref="C5:D6"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="A5:B6"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F8"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="C3:D4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="G5:J5"/>
   </mergeCells>
   <phoneticPr fontId="33" type="noConversion"/>
   <hyperlinks>
@@ -30012,142 +30012,142 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="39" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="36" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="B3" s="38" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="B4" s="38" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="B5" s="38" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="37" t="s">
+        <v>112</v>
+      </c>
+      <c r="B6" s="38" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="B7" s="38" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="37" t="s">
+        <v>115</v>
+      </c>
+      <c r="B8" s="38" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="37"/>
+      <c r="B9" s="38"/>
+    </row>
+    <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="36" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="36" t="s">
-        <v>97</v>
+    <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="37" t="s">
+        <v>90</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="37" t="s">
+      <c r="B11" s="38" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="37" t="s">
         <v>101</v>
       </c>
-      <c r="B3" s="132" t="s">
-        <v>107</v>
+      <c r="B12" s="38" t="s">
+        <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="37" t="s">
+    <row r="13" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="B13" s="38" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="37"/>
+    </row>
+    <row r="15" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="36" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="37" t="s">
         <v>98</v>
       </c>
-      <c r="B4" s="132" t="s">
-        <v>108</v>
+      <c r="B16" s="38" t="s">
+        <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="37" t="s">
-        <v>109</v>
+    <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="37" t="s">
+        <v>95</v>
       </c>
-      <c r="B5" s="132" t="s">
+      <c r="B17" s="38" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="37" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="37" t="s">
+      <c r="B18" s="38" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="37" t="s">
         <v>113</v>
       </c>
-      <c r="B6" s="132" t="s">
-        <v>122</v>
+      <c r="B19" s="38" t="s">
+        <v>114</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="37" t="s">
-        <v>120</v>
-      </c>
-      <c r="B7" s="132" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="37" t="s">
-        <v>116</v>
-      </c>
-      <c r="B8" s="132" t="s">
+    <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="37" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="37"/>
-      <c r="B9" s="132"/>
-    </row>
-    <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="36" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="B11" s="132" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="37" t="s">
-        <v>102</v>
-      </c>
-      <c r="B12" s="132" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="37" t="s">
-        <v>103</v>
-      </c>
-      <c r="B13" s="132" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="37"/>
-    </row>
-    <row r="15" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="36" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="37" t="s">
-        <v>99</v>
-      </c>
-      <c r="B16" s="132" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="B17" s="132" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="37" t="s">
-        <v>111</v>
-      </c>
-      <c r="B18" s="132" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="37" t="s">
-        <v>114</v>
-      </c>
-      <c r="B19" s="132" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="37" t="s">
+      <c r="B20" s="38" t="s">
         <v>118</v>
-      </c>
-      <c r="B20" s="132" t="s">
-        <v>119</v>
       </c>
     </row>
   </sheetData>
